--- a/2026/BRIN 3219/Mayo/BRIN3219-EXPENSAS-Mayo.xlsx
+++ b/2026/BRIN 3219/Mayo/BRIN3219-EXPENSAS-Mayo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 3219\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 3219\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBCF25E-EFB4-4869-B991-5004DC95D038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA23D9CC-4C77-4541-8401-185E1E4A0FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
@@ -19,19 +19,22 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$O$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$96</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$93</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="159">
   <si>
     <t>U.F.</t>
   </si>
@@ -346,9 +349,6 @@
   </si>
   <si>
     <t>Gabriel</t>
-  </si>
-  <si>
-    <t>Gonzalo</t>
   </si>
   <si>
     <t>Miriam</t>
@@ -498,15 +498,6 @@
     <t>Seguro - Reemplazo</t>
   </si>
   <si>
-    <t>Honorarios y aportes al Sr. Perito Mario Ruben Patitucci</t>
-  </si>
-  <si>
-    <t>Aportes Dr. Ezequiel Sarro - Sr abogado</t>
-  </si>
-  <si>
-    <t>Ezequiel Sarro - Sr Abogado - Presetacion escrito</t>
-  </si>
-  <si>
     <t>VTO: 18/06</t>
   </si>
   <si>
@@ -525,7 +516,13 @@
     <t>Cuota 2 de 5 - Limpieza de columnas, cocina y baño de todas las unidades funcionales - Cuello Natalia</t>
   </si>
   <si>
-    <t xml:space="preserve">Reparacion Heredia - </t>
+    <t xml:space="preserve">Reparacion Heredia - Trabajo integral proteccion contra roeadores, en sala de maquinas, medidores, cañerias y desagues - Limpiezas profundas, desinfeccion y retiruo de residuos </t>
+  </si>
+  <si>
+    <t>Reclamo Juidicial  en sindicato por deuda que nos reclaman mal liquidada</t>
+  </si>
+  <si>
+    <t>Acordarse de los -428650 en el resultado de la columna final de ingreso en prorrateo</t>
   </si>
 </sst>
 </file>
@@ -1341,7 +1338,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1638,9 +1635,93 @@
     <xf numFmtId="44" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1659,12 +1740,6 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1686,84 +1761,6 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1800,8 +1797,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2248,17 +2244,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:K99"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2273,23 +2269,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="205"/>
-      <c r="F2" s="205"/>
-      <c r="G2" s="205"/>
-      <c r="H2" s="206"/>
+      <c r="D2" s="199"/>
+      <c r="E2" s="200"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="200"/>
+      <c r="H2" s="201"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="208">
+      <c r="E3" s="203">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="208"/>
-      <c r="G3" s="208"/>
-      <c r="H3" s="209"/>
+      <c r="F3" s="203"/>
+      <c r="G3" s="203"/>
+      <c r="H3" s="204"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -2317,7 +2313,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H6" s="11"/>
     </row>
@@ -2325,7 +2321,7 @@
       <c r="A7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="18">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="18.75">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -2336,10 +2332,10 @@
         <v>66</v>
       </c>
       <c r="F8" s="89" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -2368,14 +2364,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="219"/>
-      <c r="B12" s="186"/>
-      <c r="C12" s="186"/>
-      <c r="D12" s="186"/>
-      <c r="E12" s="186"/>
-      <c r="F12" s="186"/>
-      <c r="G12" s="186"/>
-      <c r="H12" s="220"/>
+      <c r="A12" s="211"/>
+      <c r="B12" s="212"/>
+      <c r="C12" s="212"/>
+      <c r="D12" s="212"/>
+      <c r="E12" s="212"/>
+      <c r="F12" s="212"/>
+      <c r="G12" s="212"/>
+      <c r="H12" s="213"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2387,21 +2383,21 @@
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="15.6">
-      <c r="A14" s="221" t="s">
-        <v>122</v>
-      </c>
-      <c r="B14" s="221"/>
-      <c r="C14" s="221"/>
-      <c r="D14" s="221"/>
-      <c r="E14" s="221"/>
-      <c r="F14" s="221"/>
-      <c r="G14" s="221"/>
-      <c r="H14" s="221"/>
+    <row r="14" spans="1:9" ht="15.75">
+      <c r="A14" s="214" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="214"/>
+      <c r="C14" s="214"/>
+      <c r="D14" s="214"/>
+      <c r="E14" s="214"/>
+      <c r="F14" s="214"/>
+      <c r="G14" s="214"/>
+      <c r="H14" s="214"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="172" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B15" s="137"/>
       <c r="C15" s="137"/>
@@ -2410,7 +2406,7 @@
       <c r="F15" s="137"/>
       <c r="G15" s="137"/>
       <c r="H15" s="73">
-        <v>347680.6</v>
+        <v>358989.5</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2424,13 +2420,13 @@
       <c r="F16" s="137"/>
       <c r="G16" s="137"/>
       <c r="H16" s="73">
-        <v>-54759.7</v>
+        <v>-56540.84</v>
       </c>
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="172" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B17" s="137"/>
       <c r="C17" s="137"/>
@@ -2439,7 +2435,7 @@
       <c r="F17" s="137"/>
       <c r="G17" s="137"/>
       <c r="H17" s="73">
-        <v>0.1</v>
+        <v>0.34</v>
       </c>
       <c r="I17" s="7"/>
     </row>
@@ -2455,25 +2451,25 @@
       <c r="G18" s="137"/>
       <c r="H18" s="69">
         <f>SUM(H15:H17)</f>
-        <v>292920.99999999994</v>
+        <v>302449.00000000006</v>
       </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" hidden="1">
-      <c r="A19" s="215" t="s">
-        <v>139</v>
-      </c>
-      <c r="B19" s="215"/>
-      <c r="C19" s="215"/>
-      <c r="D19" s="215"/>
-      <c r="E19" s="215"/>
-      <c r="F19" s="215"/>
-      <c r="G19" s="215"/>
-      <c r="H19" s="215"/>
+      <c r="A19" s="207" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" s="207"/>
+      <c r="C19" s="207"/>
+      <c r="D19" s="207"/>
+      <c r="E19" s="207"/>
+      <c r="F19" s="207"/>
+      <c r="G19" s="207"/>
+      <c r="H19" s="207"/>
     </row>
     <row r="20" spans="1:9" hidden="1">
       <c r="A20" s="172" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B20" s="137"/>
       <c r="C20" s="137"/>
@@ -2487,7 +2483,7 @@
     </row>
     <row r="21" spans="1:9" hidden="1">
       <c r="A21" s="172" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B21" s="137"/>
       <c r="C21" s="137"/>
@@ -2515,20 +2511,20 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="214" t="s">
-        <v>127</v>
-      </c>
-      <c r="B23" s="214"/>
-      <c r="C23" s="214"/>
-      <c r="D23" s="214"/>
-      <c r="E23" s="214"/>
-      <c r="F23" s="214"/>
-      <c r="G23" s="214"/>
-      <c r="H23" s="214"/>
+      <c r="A23" s="206" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="206"/>
+      <c r="C23" s="206"/>
+      <c r="D23" s="206"/>
+      <c r="E23" s="206"/>
+      <c r="F23" s="206"/>
+      <c r="G23" s="206"/>
+      <c r="H23" s="206"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="137" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B24" s="137"/>
       <c r="C24" s="137"/>
@@ -2537,8 +2533,8 @@
       <c r="F24" s="137"/>
       <c r="G24" s="137"/>
       <c r="H24" s="73">
-        <f>17000+32000</f>
-        <v>49000</v>
+        <f>(17000+32000)/2</f>
+        <v>24500</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -2563,20 +2559,20 @@
       <c r="G26" s="137"/>
       <c r="H26" s="69">
         <f>SUM(H24:H25)</f>
-        <v>49000</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="207" t="s">
+      <c r="A27" s="202" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="207"/>
-      <c r="C27" s="207"/>
-      <c r="D27" s="207"/>
-      <c r="E27" s="207"/>
-      <c r="F27" s="207"/>
-      <c r="G27" s="207"/>
-      <c r="H27" s="207"/>
+      <c r="B27" s="202"/>
+      <c r="C27" s="202"/>
+      <c r="D27" s="202"/>
+      <c r="E27" s="202"/>
+      <c r="F27" s="202"/>
+      <c r="G27" s="202"/>
+      <c r="H27" s="202"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="172"/>
@@ -2598,14 +2594,14 @@
       <c r="E29" s="137"/>
       <c r="F29" s="137"/>
       <c r="G29" s="137"/>
-      <c r="H29" s="240">
+      <c r="H29" s="73">
         <f>15645.63+1738.4+27787.31</f>
         <v>45171.34</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="137" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B30" s="137"/>
       <c r="C30" s="137"/>
@@ -2633,20 +2629,20 @@
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="207" t="s">
-        <v>128</v>
-      </c>
-      <c r="B32" s="207"/>
-      <c r="C32" s="207"/>
-      <c r="D32" s="207"/>
-      <c r="E32" s="207"/>
-      <c r="F32" s="207"/>
-      <c r="G32" s="207"/>
-      <c r="H32" s="207"/>
+      <c r="A32" s="202" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="202"/>
+      <c r="C32" s="202"/>
+      <c r="D32" s="202"/>
+      <c r="E32" s="202"/>
+      <c r="F32" s="202"/>
+      <c r="G32" s="202"/>
+      <c r="H32" s="202"/>
     </row>
     <row r="33" spans="1:11" ht="14.25" customHeight="1">
       <c r="A33" s="137" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B33" s="137"/>
       <c r="C33" s="137"/>
@@ -2654,7 +2650,7 @@
       <c r="E33" s="137"/>
       <c r="F33" s="137"/>
       <c r="G33" s="137"/>
-      <c r="H33" s="240">
+      <c r="H33" s="73">
         <v>467946.31</v>
       </c>
     </row>
@@ -2668,7 +2664,7 @@
       <c r="E34" s="137"/>
       <c r="F34" s="137"/>
       <c r="G34" s="137"/>
-      <c r="H34" s="240">
+      <c r="H34" s="73">
         <v>57718.38</v>
       </c>
     </row>
@@ -2688,16 +2684,16 @@
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="221" t="s">
-        <v>129</v>
-      </c>
-      <c r="B36" s="221"/>
-      <c r="C36" s="221"/>
-      <c r="D36" s="221"/>
-      <c r="E36" s="221"/>
-      <c r="F36" s="221"/>
-      <c r="G36" s="221"/>
-      <c r="H36" s="221"/>
+      <c r="A36" s="214" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" s="214"/>
+      <c r="C36" s="214"/>
+      <c r="D36" s="214"/>
+      <c r="E36" s="214"/>
+      <c r="F36" s="214"/>
+      <c r="G36" s="214"/>
+      <c r="H36" s="214"/>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="80" t="s">
@@ -2709,13 +2705,13 @@
       <c r="E37" s="137"/>
       <c r="F37" s="137"/>
       <c r="G37" s="137"/>
-      <c r="H37" s="240">
+      <c r="H37" s="73">
         <v>93200</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="80" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B38" s="137"/>
       <c r="C38" s="137"/>
@@ -2728,17 +2724,17 @@
       </c>
       <c r="I38" s="7"/>
     </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="241" t="s">
-        <v>160</v>
-      </c>
-      <c r="B39" s="137"/>
-      <c r="C39" s="137"/>
-      <c r="D39" s="137"/>
-      <c r="E39" s="137"/>
-      <c r="F39" s="137"/>
-      <c r="G39" s="137"/>
-      <c r="H39" s="240">
+    <row r="39" spans="1:11" ht="36" customHeight="1">
+      <c r="A39" s="208" t="s">
+        <v>156</v>
+      </c>
+      <c r="B39" s="209"/>
+      <c r="C39" s="209"/>
+      <c r="D39" s="209"/>
+      <c r="E39" s="209"/>
+      <c r="F39" s="209"/>
+      <c r="G39" s="210"/>
+      <c r="H39" s="73">
         <v>213000</v>
       </c>
       <c r="I39" s="7"/>
@@ -2753,13 +2749,13 @@
       <c r="E40" s="137"/>
       <c r="F40" s="137"/>
       <c r="G40" s="137"/>
-      <c r="H40" s="240">
+      <c r="H40" s="73">
         <v>26301.21</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="137" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B41" s="137"/>
       <c r="C41" s="137"/>
@@ -2767,13 +2763,13 @@
       <c r="E41" s="137"/>
       <c r="F41" s="137"/>
       <c r="G41" s="137"/>
-      <c r="H41" s="240">
+      <c r="H41" s="73">
         <v>1783159.87</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="137" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B42" s="137"/>
       <c r="C42" s="137"/>
@@ -2781,13 +2777,13 @@
       <c r="E42" s="137"/>
       <c r="F42" s="137"/>
       <c r="G42" s="137"/>
-      <c r="H42" s="240">
+      <c r="H42" s="73">
         <v>65000</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="137" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B43" s="137"/>
       <c r="C43" s="137"/>
@@ -2795,7 +2791,7 @@
       <c r="E43" s="137"/>
       <c r="F43" s="137"/>
       <c r="G43" s="137"/>
-      <c r="H43" s="240">
+      <c r="H43" s="73">
         <v>413700</v>
       </c>
     </row>
@@ -2815,16 +2811,16 @@
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="221" t="s">
-        <v>130</v>
-      </c>
-      <c r="B45" s="221"/>
-      <c r="C45" s="221"/>
-      <c r="D45" s="221"/>
-      <c r="E45" s="221"/>
-      <c r="F45" s="221"/>
-      <c r="G45" s="221"/>
-      <c r="H45" s="221"/>
+      <c r="A45" s="214" t="s">
+        <v>129</v>
+      </c>
+      <c r="B45" s="214"/>
+      <c r="C45" s="214"/>
+      <c r="D45" s="214"/>
+      <c r="E45" s="214"/>
+      <c r="F45" s="214"/>
+      <c r="G45" s="214"/>
+      <c r="H45" s="214"/>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="137" t="s">
@@ -2840,12 +2836,12 @@
         <v>189700</v>
       </c>
       <c r="J46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="137" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B47" s="137"/>
       <c r="C47" s="137"/>
@@ -2853,7 +2849,7 @@
       <c r="E47" s="137"/>
       <c r="F47" s="137"/>
       <c r="G47" s="137"/>
-      <c r="H47" s="240">
+      <c r="H47" s="73">
         <v>45000</v>
       </c>
     </row>
@@ -2874,20 +2870,20 @@
       <c r="K48" s="7"/>
     </row>
     <row r="49" spans="1:9" s="6" customFormat="1">
-      <c r="A49" s="222" t="s">
-        <v>131</v>
-      </c>
-      <c r="B49" s="223"/>
-      <c r="C49" s="223"/>
-      <c r="D49" s="223"/>
-      <c r="E49" s="223"/>
-      <c r="F49" s="223"/>
-      <c r="G49" s="223"/>
-      <c r="H49" s="224"/>
+      <c r="A49" s="186" t="s">
+        <v>130</v>
+      </c>
+      <c r="B49" s="187"/>
+      <c r="C49" s="187"/>
+      <c r="D49" s="187"/>
+      <c r="E49" s="187"/>
+      <c r="F49" s="187"/>
+      <c r="G49" s="187"/>
+      <c r="H49" s="188"/>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1">
       <c r="A50" s="80" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B50" s="80"/>
       <c r="C50" s="80"/>
@@ -2895,7 +2891,7 @@
       <c r="E50" s="80"/>
       <c r="F50" s="80"/>
       <c r="G50" s="80"/>
-      <c r="H50" s="240">
+      <c r="H50" s="73">
         <v>26307</v>
       </c>
       <c r="I50" s="60"/>
@@ -2916,20 +2912,20 @@
       </c>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1">
-      <c r="A52" s="221" t="s">
-        <v>132</v>
-      </c>
-      <c r="B52" s="221"/>
-      <c r="C52" s="221"/>
-      <c r="D52" s="221"/>
-      <c r="E52" s="221"/>
-      <c r="F52" s="221"/>
-      <c r="G52" s="221"/>
-      <c r="H52" s="221"/>
+      <c r="A52" s="214" t="s">
+        <v>131</v>
+      </c>
+      <c r="B52" s="214"/>
+      <c r="C52" s="214"/>
+      <c r="D52" s="214"/>
+      <c r="E52" s="214"/>
+      <c r="F52" s="214"/>
+      <c r="G52" s="214"/>
+      <c r="H52" s="214"/>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1">
       <c r="A53" s="80" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B53" s="80"/>
       <c r="C53" s="80"/>
@@ -2938,13 +2934,12 @@
       <c r="F53" s="80"/>
       <c r="G53" s="80"/>
       <c r="H53" s="73">
-        <f>97952+30365</f>
-        <v>128317</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="6" customFormat="1">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="80" t="s">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="B54" s="80"/>
       <c r="C54" s="80"/>
@@ -2952,292 +2947,286 @@
       <c r="E54" s="80"/>
       <c r="F54" s="80"/>
       <c r="G54" s="80"/>
-      <c r="H54" s="73">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" s="6" customFormat="1">
-      <c r="A55" s="80" t="s">
-        <v>152</v>
-      </c>
-      <c r="B55" s="80"/>
-      <c r="C55" s="80"/>
-      <c r="D55" s="80"/>
-      <c r="E55" s="80"/>
-      <c r="F55" s="80"/>
-      <c r="G55" s="80"/>
-      <c r="H55" s="73">
-        <v>49750</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" s="6" customFormat="1" ht="15" customHeight="1">
-      <c r="A56" s="80" t="s">
-        <v>74</v>
-      </c>
-      <c r="B56" s="80"/>
-      <c r="C56" s="80"/>
-      <c r="D56" s="80"/>
-      <c r="E56" s="80"/>
-      <c r="F56" s="80"/>
-      <c r="G56" s="80"/>
-      <c r="H56" s="69">
-        <f>SUM(H53:H55)</f>
-        <v>278067</v>
-      </c>
-      <c r="I56" s="60"/>
-    </row>
-    <row r="57" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A57" s="222"/>
-      <c r="B57" s="223"/>
-      <c r="C57" s="223"/>
-      <c r="D57" s="223"/>
-      <c r="E57" s="223"/>
-      <c r="F57" s="223"/>
-      <c r="G57" s="223"/>
-      <c r="H57" s="224"/>
-    </row>
-    <row r="58" spans="1:9" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A58" s="81"/>
-      <c r="B58" s="82"/>
-      <c r="C58" s="82"/>
-      <c r="D58" s="82"/>
-      <c r="E58" s="82"/>
-      <c r="F58" s="82"/>
-      <c r="G58" s="82"/>
+      <c r="H54" s="69">
+        <f>SUM(H53:H53)</f>
+        <v>80000</v>
+      </c>
+      <c r="I54" s="60"/>
+    </row>
+    <row r="55" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A55" s="186"/>
+      <c r="B55" s="187"/>
+      <c r="C55" s="187"/>
+      <c r="D55" s="187"/>
+      <c r="E55" s="187"/>
+      <c r="F55" s="187"/>
+      <c r="G55" s="187"/>
+      <c r="H55" s="188"/>
+    </row>
+    <row r="56" spans="1:9" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A56" s="81"/>
+      <c r="B56" s="82"/>
+      <c r="C56" s="82"/>
+      <c r="D56" s="82"/>
+      <c r="E56" s="82"/>
+      <c r="F56" s="82"/>
+      <c r="G56" s="82"/>
+      <c r="H56" s="156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A57" s="157"/>
+      <c r="B57" s="158"/>
+      <c r="C57" s="158"/>
+      <c r="D57" s="158"/>
+      <c r="E57" s="158"/>
+      <c r="F57" s="158"/>
+      <c r="G57" s="158"/>
+      <c r="H57" s="159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A58" s="160"/>
+      <c r="B58" s="161"/>
+      <c r="C58" s="161"/>
+      <c r="D58" s="161"/>
+      <c r="E58" s="161"/>
+      <c r="F58" s="161"/>
+      <c r="G58" s="161"/>
       <c r="H58" s="156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A59" s="157"/>
-      <c r="B59" s="158"/>
-      <c r="C59" s="158"/>
-      <c r="D59" s="158"/>
-      <c r="E59" s="158"/>
-      <c r="F59" s="158"/>
-      <c r="G59" s="158"/>
-      <c r="H59" s="159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A60" s="160"/>
-      <c r="B60" s="161"/>
-      <c r="C60" s="161"/>
-      <c r="D60" s="161"/>
-      <c r="E60" s="161"/>
-      <c r="F60" s="161"/>
-      <c r="G60" s="161"/>
-      <c r="H60" s="156">
-        <f>H58+H59</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A61" s="225" t="s">
+        <f>H56+H57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A59" s="192" t="s">
         <v>80</v>
       </c>
-      <c r="B61" s="226"/>
-      <c r="C61" s="226"/>
-      <c r="D61" s="226"/>
-      <c r="E61" s="226"/>
-      <c r="F61" s="226"/>
-      <c r="G61" s="226"/>
-      <c r="H61" s="162">
-        <f>H56</f>
-        <v>278067</v>
-      </c>
+      <c r="B59" s="193"/>
+      <c r="C59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="162">
+        <f>H54</f>
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A60" s="197"/>
+      <c r="B60" s="197"/>
+      <c r="C60" s="197"/>
+      <c r="D60" s="197"/>
+      <c r="E60" s="197"/>
+      <c r="F60" s="197"/>
+      <c r="G60" s="197"/>
+      <c r="H60" s="197"/>
+    </row>
+    <row r="61" spans="1:9" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A61" s="198"/>
+      <c r="B61" s="198"/>
+      <c r="C61" s="198"/>
+      <c r="D61" s="198"/>
+      <c r="E61" s="198"/>
+      <c r="F61" s="198"/>
+      <c r="G61" s="198"/>
+      <c r="H61" s="198"/>
     </row>
     <row r="62" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A62" s="202"/>
-      <c r="B62" s="202"/>
-      <c r="C62" s="202"/>
-      <c r="D62" s="202"/>
-      <c r="E62" s="202"/>
-      <c r="F62" s="202"/>
-      <c r="G62" s="202"/>
-      <c r="H62" s="202"/>
-    </row>
-    <row r="63" spans="1:9" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A63" s="203"/>
-      <c r="B63" s="203"/>
-      <c r="C63" s="203"/>
-      <c r="D63" s="203"/>
-      <c r="E63" s="203"/>
-      <c r="F63" s="203"/>
-      <c r="G63" s="203"/>
-      <c r="H63" s="203"/>
+      <c r="A62" s="196" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" s="196"/>
+      <c r="C62" s="196"/>
+      <c r="D62" s="196"/>
+      <c r="E62" s="196"/>
+      <c r="F62" s="196"/>
+      <c r="G62" s="196"/>
+      <c r="H62" s="163"/>
+    </row>
+    <row r="63" spans="1:9" s="6" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A63" s="208"/>
+      <c r="B63" s="209"/>
+      <c r="C63" s="209"/>
+      <c r="D63" s="209"/>
+      <c r="E63" s="209"/>
+      <c r="F63" s="209"/>
+      <c r="G63" s="210"/>
+      <c r="H63" s="73"/>
     </row>
     <row r="64" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A64" s="227" t="s">
-        <v>82</v>
-      </c>
-      <c r="B64" s="227"/>
-      <c r="C64" s="227"/>
-      <c r="D64" s="227"/>
-      <c r="E64" s="227"/>
-      <c r="F64" s="227"/>
-      <c r="G64" s="227"/>
-      <c r="H64" s="163"/>
-    </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A65" s="216"/>
-      <c r="B65" s="217"/>
-      <c r="C65" s="217"/>
-      <c r="D65" s="217"/>
-      <c r="E65" s="217"/>
-      <c r="F65" s="217"/>
-      <c r="G65" s="218"/>
-      <c r="H65" s="73"/>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A66" s="127" t="s">
+      <c r="A64" s="127" t="s">
         <v>73</v>
       </c>
-      <c r="B66" s="80"/>
-      <c r="C66" s="80"/>
-      <c r="D66" s="80"/>
-      <c r="E66" s="80"/>
-      <c r="F66" s="80"/>
-      <c r="G66" s="80"/>
-      <c r="H66" s="69">
-        <f>SUM(H65:H65)</f>
+      <c r="B64" s="80"/>
+      <c r="C64" s="80"/>
+      <c r="D64" s="80"/>
+      <c r="E64" s="80"/>
+      <c r="F64" s="80"/>
+      <c r="G64" s="80"/>
+      <c r="H64" s="69">
+        <f>SUM(H63:H63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A65" s="128"/>
+      <c r="B65" s="128"/>
+      <c r="C65" s="128"/>
+      <c r="D65" s="128"/>
+      <c r="E65" s="128"/>
+      <c r="F65" s="128"/>
+      <c r="G65" s="128"/>
+      <c r="H65" s="129"/>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A66" s="194" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="195"/>
+      <c r="C66" s="195"/>
+      <c r="D66" s="195"/>
+      <c r="E66" s="195"/>
+      <c r="F66" s="195"/>
+      <c r="G66" s="195"/>
+      <c r="H66" s="130">
+        <f>H64</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A67" s="128"/>
-      <c r="B67" s="128"/>
-      <c r="C67" s="128"/>
-      <c r="D67" s="128"/>
-      <c r="E67" s="128"/>
-      <c r="F67" s="128"/>
-      <c r="G67" s="128"/>
-      <c r="H67" s="129"/>
+      <c r="A67" s="189" t="s">
+        <v>87</v>
+      </c>
+      <c r="B67" s="190"/>
+      <c r="C67" s="190"/>
+      <c r="D67" s="190"/>
+      <c r="E67" s="190"/>
+      <c r="F67" s="190"/>
+      <c r="G67" s="191"/>
+      <c r="H67" s="130"/>
     </row>
     <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A68" s="193" t="s">
-        <v>81</v>
-      </c>
-      <c r="B68" s="194"/>
-      <c r="C68" s="194"/>
-      <c r="D68" s="194"/>
-      <c r="E68" s="194"/>
-      <c r="F68" s="194"/>
-      <c r="G68" s="194"/>
-      <c r="H68" s="130">
-        <f>H66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A69" s="211" t="s">
-        <v>87</v>
-      </c>
-      <c r="B69" s="212"/>
-      <c r="C69" s="212"/>
-      <c r="D69" s="212"/>
-      <c r="E69" s="212"/>
-      <c r="F69" s="212"/>
-      <c r="G69" s="213"/>
-      <c r="H69" s="130"/>
-    </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A70" s="211" t="s">
+      <c r="A68" s="189" t="s">
         <v>92</v>
       </c>
-      <c r="B70" s="212"/>
-      <c r="C70" s="212"/>
-      <c r="D70" s="212"/>
-      <c r="E70" s="212"/>
-      <c r="F70" s="212"/>
-      <c r="G70" s="213"/>
-      <c r="H70" s="130"/>
-    </row>
-    <row r="71" spans="1:11" ht="18">
-      <c r="A71" s="193" t="s">
+      <c r="B68" s="190"/>
+      <c r="C68" s="190"/>
+      <c r="D68" s="190"/>
+      <c r="E68" s="190"/>
+      <c r="F68" s="190"/>
+      <c r="G68" s="191"/>
+      <c r="H68" s="130"/>
+    </row>
+    <row r="69" spans="1:11" ht="18.75">
+      <c r="A69" s="194" t="s">
         <v>88</v>
       </c>
-      <c r="B71" s="194"/>
-      <c r="C71" s="194"/>
-      <c r="D71" s="194"/>
-      <c r="E71" s="194"/>
-      <c r="F71" s="194"/>
-      <c r="G71" s="194"/>
-      <c r="H71" s="130">
+      <c r="B69" s="195"/>
+      <c r="C69" s="195"/>
+      <c r="D69" s="195"/>
+      <c r="E69" s="195"/>
+      <c r="F69" s="195"/>
+      <c r="G69" s="195"/>
+      <c r="H69" s="130">
         <f>H26+H35+H44+H48+H51+H31+H18+H22</f>
-        <v>3768125.11</v>
-      </c>
-      <c r="J71" s="171"/>
-      <c r="K71" s="142"/>
-    </row>
-    <row r="72" spans="1:11" ht="18">
-      <c r="A72" s="199" t="s">
-        <v>120</v>
-      </c>
-      <c r="B72" s="200"/>
-      <c r="C72" s="200"/>
-      <c r="D72" s="200"/>
-      <c r="E72" s="200"/>
-      <c r="F72" s="200"/>
-      <c r="G72" s="201"/>
-      <c r="H72" s="131">
-        <f>H69+H71</f>
-        <v>3768125.11</v>
-      </c>
-      <c r="I72" s="126"/>
-      <c r="J72" s="210"/>
-      <c r="K72" s="210"/>
-    </row>
-    <row r="73" spans="1:11" ht="18">
-      <c r="A73" s="199" t="s">
+        <v>3753153.11</v>
+      </c>
+      <c r="J69" s="171"/>
+      <c r="K69" s="142"/>
+    </row>
+    <row r="70" spans="1:11" ht="18.75">
+      <c r="A70" s="225" t="s">
+        <v>119</v>
+      </c>
+      <c r="B70" s="226"/>
+      <c r="C70" s="226"/>
+      <c r="D70" s="226"/>
+      <c r="E70" s="226"/>
+      <c r="F70" s="226"/>
+      <c r="G70" s="227"/>
+      <c r="H70" s="131">
+        <f>H67+H69</f>
+        <v>3753153.11</v>
+      </c>
+      <c r="I70" s="126"/>
+      <c r="J70" s="205"/>
+      <c r="K70" s="205"/>
+    </row>
+    <row r="71" spans="1:11" ht="18.75">
+      <c r="A71" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="B73" s="200"/>
-      <c r="C73" s="200"/>
-      <c r="D73" s="200"/>
-      <c r="E73" s="200"/>
-      <c r="F73" s="200"/>
-      <c r="G73" s="201"/>
-      <c r="H73" s="132">
-        <f>H70+H68</f>
-        <v>0</v>
-      </c>
-      <c r="J73" s="142"/>
-    </row>
-    <row r="74" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A74" s="197" t="s">
+      <c r="B71" s="226"/>
+      <c r="C71" s="226"/>
+      <c r="D71" s="226"/>
+      <c r="E71" s="226"/>
+      <c r="F71" s="226"/>
+      <c r="G71" s="227"/>
+      <c r="H71" s="132">
+        <f>H68+H66</f>
+        <v>0</v>
+      </c>
+      <c r="J71" s="142"/>
+    </row>
+    <row r="72" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A72" s="223" t="s">
         <v>83</v>
       </c>
-      <c r="B74" s="198"/>
-      <c r="C74" s="198"/>
-      <c r="D74" s="198"/>
-      <c r="E74" s="198"/>
-      <c r="F74" s="198"/>
-      <c r="G74" s="198"/>
-      <c r="H74" s="133">
-        <f>H71+H68</f>
-        <v>3768125.11</v>
-      </c>
+      <c r="B72" s="224"/>
+      <c r="C72" s="224"/>
+      <c r="D72" s="224"/>
+      <c r="E72" s="224"/>
+      <c r="F72" s="224"/>
+      <c r="G72" s="224"/>
+      <c r="H72" s="133">
+        <f>H69+H66</f>
+        <v>3753153.11</v>
+      </c>
+      <c r="J72" s="7"/>
+    </row>
+    <row r="73" spans="1:11" ht="18.75" hidden="1">
+      <c r="A73" s="221" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73" s="222"/>
+      <c r="C73" s="222"/>
+      <c r="D73" s="222"/>
+      <c r="E73" s="222"/>
+      <c r="F73" s="222"/>
+      <c r="G73" s="222"/>
+      <c r="H73" s="134">
+        <f>H58</f>
+        <v>0</v>
+      </c>
+      <c r="J73" s="7"/>
+    </row>
+    <row r="74" spans="1:11" ht="18.75" hidden="1">
+      <c r="A74" s="135"/>
+      <c r="B74" s="135"/>
+      <c r="C74" s="135"/>
+      <c r="D74" s="135"/>
+      <c r="E74" s="135"/>
+      <c r="F74" s="135"/>
+      <c r="G74" s="135"/>
+      <c r="H74" s="136"/>
       <c r="J74" s="7"/>
     </row>
-    <row r="75" spans="1:11" ht="18" hidden="1">
-      <c r="A75" s="195" t="s">
-        <v>17</v>
-      </c>
-      <c r="B75" s="196"/>
-      <c r="C75" s="196"/>
-      <c r="D75" s="196"/>
-      <c r="E75" s="196"/>
-      <c r="F75" s="196"/>
-      <c r="G75" s="196"/>
-      <c r="H75" s="134">
-        <f>H60</f>
-        <v>0</v>
-      </c>
+    <row r="75" spans="1:11" ht="18.75" hidden="1">
+      <c r="A75" s="135"/>
+      <c r="B75" s="135"/>
+      <c r="C75" s="135"/>
+      <c r="D75" s="135"/>
+      <c r="E75" s="135"/>
+      <c r="F75" s="135"/>
+      <c r="G75" s="135"/>
+      <c r="H75" s="136"/>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="1:11" ht="18" hidden="1">
+    <row r="76" spans="1:11" ht="18.75" hidden="1">
       <c r="A76" s="135"/>
       <c r="B76" s="135"/>
       <c r="C76" s="135"/>
@@ -3248,82 +3237,94 @@
       <c r="H76" s="136"/>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" spans="1:11" ht="18" hidden="1">
-      <c r="A77" s="135"/>
-      <c r="B77" s="135"/>
-      <c r="C77" s="135"/>
-      <c r="D77" s="135"/>
-      <c r="E77" s="135"/>
-      <c r="F77" s="135"/>
-      <c r="G77" s="135"/>
-      <c r="H77" s="136"/>
-      <c r="J77" s="7"/>
-    </row>
-    <row r="78" spans="1:11" ht="18" hidden="1">
-      <c r="A78" s="135"/>
-      <c r="B78" s="135"/>
-      <c r="C78" s="135"/>
-      <c r="D78" s="135"/>
-      <c r="E78" s="135"/>
-      <c r="F78" s="135"/>
-      <c r="G78" s="135"/>
-      <c r="H78" s="136"/>
-      <c r="J78" s="7"/>
-    </row>
-    <row r="79" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A79" s="137"/>
-      <c r="B79" s="137"/>
-      <c r="C79" s="137"/>
-      <c r="D79" s="137"/>
-      <c r="E79" s="137"/>
-      <c r="F79" s="137"/>
-      <c r="G79" s="137"/>
-      <c r="H79" s="137"/>
-    </row>
-    <row r="80" spans="1:11" ht="18">
-      <c r="A80" s="190" t="s">
+    <row r="77" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A77" s="137"/>
+      <c r="B77" s="137"/>
+      <c r="C77" s="137"/>
+      <c r="D77" s="137"/>
+      <c r="E77" s="137"/>
+      <c r="F77" s="137"/>
+      <c r="G77" s="137"/>
+      <c r="H77" s="137"/>
+    </row>
+    <row r="78" spans="1:11" ht="18.75">
+      <c r="A78" s="218" t="s">
         <v>10</v>
       </c>
-      <c r="B80" s="191"/>
-      <c r="C80" s="191"/>
-      <c r="D80" s="191"/>
-      <c r="E80" s="191"/>
-      <c r="F80" s="191"/>
-      <c r="G80" s="191"/>
-      <c r="H80" s="192"/>
-    </row>
-    <row r="81" spans="1:11" ht="18">
-      <c r="A81" s="138" t="s">
+      <c r="B78" s="219"/>
+      <c r="C78" s="219"/>
+      <c r="D78" s="219"/>
+      <c r="E78" s="219"/>
+      <c r="F78" s="219"/>
+      <c r="G78" s="219"/>
+      <c r="H78" s="220"/>
+    </row>
+    <row r="79" spans="1:11" ht="18.75">
+      <c r="A79" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="B81" s="139"/>
-      <c r="C81" s="139"/>
-      <c r="D81" s="139"/>
-      <c r="E81" s="139"/>
-      <c r="F81" s="139"/>
-      <c r="G81" s="139"/>
-      <c r="H81" s="140">
-        <v>7329447.2949116919</v>
+      <c r="B79" s="139"/>
+      <c r="C79" s="139"/>
+      <c r="D79" s="139"/>
+      <c r="E79" s="139"/>
+      <c r="F79" s="139"/>
+      <c r="G79" s="139"/>
+      <c r="H79" s="140">
+        <v>6822922.8199556917</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="81" t="s">
+        <v>145</v>
+      </c>
+      <c r="B80" s="82"/>
+      <c r="C80" s="82"/>
+      <c r="D80" s="82"/>
+      <c r="E80" s="82"/>
+      <c r="F80" s="82"/>
+      <c r="G80" s="82"/>
+      <c r="H80" s="141">
+        <f>Planilla!G32</f>
+        <v>1554352.4065020001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="78" t="s">
+        <v>153</v>
+      </c>
+      <c r="B81" s="79"/>
+      <c r="C81" s="79"/>
+      <c r="D81" s="79"/>
+      <c r="E81" s="79"/>
+      <c r="F81" s="79"/>
+      <c r="G81" s="79"/>
+      <c r="H81" s="179">
+        <f>-(H72)</f>
+        <v>-3753153.11</v>
       </c>
     </row>
     <row r="82" spans="1:11">
-      <c r="A82" s="81" t="s">
-        <v>146</v>
-      </c>
-      <c r="B82" s="82"/>
-      <c r="C82" s="82"/>
-      <c r="D82" s="82"/>
-      <c r="E82" s="82"/>
-      <c r="F82" s="82"/>
-      <c r="G82" s="82"/>
-      <c r="H82" s="141">
-        <f>Planilla!G32</f>
-        <v>1983592.6250439996</v>
-      </c>
+      <c r="A82" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="B82" s="79"/>
+      <c r="C82" s="79"/>
+      <c r="D82" s="79"/>
+      <c r="E82" s="79"/>
+      <c r="F82" s="79"/>
+      <c r="G82" s="79"/>
+      <c r="H82" s="179">
+        <f>-H59</f>
+        <v>-80000</v>
+      </c>
+      <c r="J82" s="240" t="s">
+        <v>158</v>
+      </c>
+      <c r="K82" s="6"/>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="78" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="B83" s="79"/>
       <c r="C83" s="79"/>
@@ -3331,14 +3332,14 @@
       <c r="E83" s="79"/>
       <c r="F83" s="79"/>
       <c r="G83" s="79"/>
-      <c r="H83" s="179">
-        <f>-(H74)</f>
-        <v>-3768125.11</v>
-      </c>
+      <c r="H83" s="121">
+        <v>133680</v>
+      </c>
+      <c r="J83" s="7"/>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="78" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="B84" s="79"/>
       <c r="C84" s="79"/>
@@ -3346,216 +3347,186 @@
       <c r="E84" s="79"/>
       <c r="F84" s="79"/>
       <c r="G84" s="79"/>
-      <c r="H84" s="179">
-        <f>-H61</f>
-        <v>-278067</v>
-      </c>
-      <c r="K84" s="6"/>
+      <c r="H84" s="121">
+        <f>180000-H83</f>
+        <v>46320</v>
+      </c>
+      <c r="I84" s="142"/>
+      <c r="J84" s="7"/>
     </row>
     <row r="85" spans="1:11">
-      <c r="A85" s="78" t="s">
-        <v>145</v>
-      </c>
-      <c r="B85" s="79"/>
-      <c r="C85" s="79"/>
-      <c r="D85" s="79"/>
-      <c r="E85" s="79"/>
-      <c r="F85" s="79"/>
-      <c r="G85" s="79"/>
-      <c r="H85" s="121">
-        <v>133680</v>
-      </c>
-      <c r="J85" s="7"/>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="78" t="s">
-        <v>71</v>
-      </c>
-      <c r="B86" s="79"/>
-      <c r="C86" s="79"/>
-      <c r="D86" s="79"/>
-      <c r="E86" s="79"/>
-      <c r="F86" s="79"/>
-      <c r="G86" s="79"/>
-      <c r="H86" s="121">
-        <f>180000-H85</f>
-        <v>46320</v>
-      </c>
-      <c r="I86" s="142"/>
-      <c r="J86" s="7"/>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="12" t="s">
+      <c r="A85" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B85" s="83"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="98"/>
+    </row>
+    <row r="86" spans="1:11" ht="18.75">
+      <c r="A86" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" s="23"/>
+      <c r="C86" s="23"/>
+      <c r="D86" s="23"/>
+      <c r="E86" s="23"/>
+      <c r="F86" s="23"/>
+      <c r="G86" s="23"/>
+      <c r="H86" s="84">
+        <f>SUM(H79:H85)</f>
+        <v>4724122.1164576914</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="88" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A88" s="215" t="s">
+        <v>97</v>
+      </c>
+      <c r="B88" s="216"/>
+      <c r="C88" s="216"/>
+      <c r="D88" s="216"/>
+      <c r="E88" s="216"/>
+      <c r="F88" s="216"/>
+      <c r="G88" s="216"/>
+      <c r="H88" s="217"/>
+    </row>
+    <row r="89" spans="1:11" ht="15.75">
+      <c r="A89" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="B89" s="87"/>
+      <c r="C89" s="87"/>
+      <c r="D89" s="87"/>
+      <c r="E89" s="87"/>
+      <c r="F89" s="87"/>
+      <c r="G89" s="87"/>
+      <c r="H89" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="B87" s="83"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="98"/>
-    </row>
-    <row r="88" spans="1:11" ht="18">
-      <c r="A88" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B88" s="23"/>
-      <c r="C88" s="23"/>
-      <c r="D88" s="23"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="23"/>
-      <c r="G88" s="23"/>
-      <c r="H88" s="84">
-        <f>SUM(H81:H87)</f>
-        <v>5446847.8099556919</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="15" thickBot="1"/>
-    <row r="90" spans="1:11" ht="16.2" thickBot="1">
-      <c r="A90" s="187" t="s">
-        <v>97</v>
-      </c>
-      <c r="B90" s="188"/>
-      <c r="C90" s="188"/>
-      <c r="D90" s="188"/>
-      <c r="E90" s="188"/>
-      <c r="F90" s="188"/>
-      <c r="G90" s="188"/>
-      <c r="H90" s="189"/>
-    </row>
-    <row r="91" spans="1:11" ht="15.6">
-      <c r="A91" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="B91" s="87"/>
-      <c r="C91" s="87"/>
-      <c r="D91" s="87"/>
-      <c r="E91" s="87"/>
-      <c r="F91" s="87"/>
-      <c r="G91" s="87"/>
-      <c r="H91" s="88">
-        <v>0</v>
-      </c>
+      <c r="B90" s="91"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="61"/>
+      <c r="E90" s="61"/>
+      <c r="F90" s="61"/>
+      <c r="G90" s="61"/>
+      <c r="H90" s="125"/>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="61"/>
+      <c r="B91" s="97"/>
+      <c r="C91" s="61"/>
+      <c r="D91" s="61"/>
+      <c r="E91" s="61"/>
+      <c r="F91" s="61"/>
+      <c r="G91" s="61"/>
+      <c r="H91" s="21"/>
     </row>
     <row r="92" spans="1:11">
-      <c r="A92" s="61" t="s">
-        <v>119</v>
-      </c>
-      <c r="B92" s="91"/>
-      <c r="C92" s="4"/>
+      <c r="A92" s="61"/>
+      <c r="B92" s="61"/>
+      <c r="C92" s="61"/>
       <c r="D92" s="61"/>
       <c r="E92" s="61"/>
       <c r="F92" s="61"/>
       <c r="G92" s="61"/>
-      <c r="H92" s="125"/>
+      <c r="H92" s="21"/>
     </row>
     <row r="93" spans="1:11">
-      <c r="A93" s="61"/>
-      <c r="B93" s="97"/>
-      <c r="C93" s="61"/>
-      <c r="D93" s="61"/>
-      <c r="E93" s="61"/>
-      <c r="F93" s="61"/>
-      <c r="G93" s="61"/>
-      <c r="H93" s="21"/>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="61"/>
-      <c r="B94" s="61"/>
-      <c r="C94" s="61"/>
-      <c r="D94" s="61"/>
-      <c r="E94" s="61"/>
-      <c r="F94" s="61"/>
-      <c r="G94" s="61"/>
-      <c r="H94" s="21"/>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" s="85" t="s">
+      <c r="A93" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="B95" s="85"/>
-      <c r="C95" s="85"/>
-      <c r="D95" s="85"/>
-      <c r="E95" s="85"/>
-      <c r="F95" s="85"/>
-      <c r="G95" s="85"/>
-      <c r="H95" s="86">
-        <f>SUM(H91:H94)</f>
-        <v>0</v>
-      </c>
+      <c r="B93" s="85"/>
+      <c r="C93" s="85"/>
+      <c r="D93" s="85"/>
+      <c r="E93" s="85"/>
+      <c r="F93" s="85"/>
+      <c r="G93" s="85"/>
+      <c r="H93" s="86">
+        <f>SUM(H89:H92)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" hidden="1">
+      <c r="A96" s="212"/>
+      <c r="B96" s="212"/>
+      <c r="C96" s="212"/>
+      <c r="D96" s="212"/>
+      <c r="E96" s="212"/>
+      <c r="F96" s="212"/>
+      <c r="G96" s="212"/>
+      <c r="H96" s="212"/>
+    </row>
+    <row r="97" spans="1:8" hidden="1">
+      <c r="A97" s="212"/>
+      <c r="B97" s="212"/>
+      <c r="C97" s="212"/>
+      <c r="D97" s="212"/>
+      <c r="E97" s="212"/>
+      <c r="F97" s="212"/>
+      <c r="G97" s="212"/>
+      <c r="H97" s="212"/>
     </row>
     <row r="98" spans="1:8" hidden="1">
-      <c r="A98" s="186"/>
-      <c r="B98" s="186"/>
-      <c r="C98" s="186"/>
-      <c r="D98" s="186"/>
-      <c r="E98" s="186"/>
-      <c r="F98" s="186"/>
-      <c r="G98" s="186"/>
-      <c r="H98" s="186"/>
+      <c r="A98" s="212"/>
+      <c r="B98" s="212"/>
+      <c r="C98" s="212"/>
+      <c r="D98" s="212"/>
+      <c r="E98" s="212"/>
+      <c r="F98" s="212"/>
+      <c r="G98" s="212"/>
+      <c r="H98" s="212"/>
     </row>
     <row r="99" spans="1:8" hidden="1">
-      <c r="A99" s="186"/>
-      <c r="B99" s="186"/>
-      <c r="C99" s="186"/>
-      <c r="D99" s="186"/>
-      <c r="E99" s="186"/>
-      <c r="F99" s="186"/>
-      <c r="G99" s="186"/>
-      <c r="H99" s="186"/>
-    </row>
-    <row r="100" spans="1:8" hidden="1">
-      <c r="A100" s="186"/>
-      <c r="B100" s="186"/>
-      <c r="C100" s="186"/>
-      <c r="D100" s="186"/>
-      <c r="E100" s="186"/>
-      <c r="F100" s="186"/>
-      <c r="G100" s="186"/>
-      <c r="H100" s="186"/>
-    </row>
-    <row r="101" spans="1:8" hidden="1">
-      <c r="A101" s="186"/>
-      <c r="B101" s="186"/>
-      <c r="C101" s="186"/>
-      <c r="D101" s="186"/>
-      <c r="E101" s="186"/>
-      <c r="F101" s="186"/>
-      <c r="G101" s="186"/>
-      <c r="H101" s="186"/>
+      <c r="A99" s="212"/>
+      <c r="B99" s="212"/>
+      <c r="C99" s="212"/>
+      <c r="D99" s="212"/>
+      <c r="E99" s="212"/>
+      <c r="F99" s="212"/>
+      <c r="G99" s="212"/>
+      <c r="H99" s="212"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A49:H49"/>
+  <mergeCells count="30">
+    <mergeCell ref="A96:H99"/>
+    <mergeCell ref="A88:H88"/>
+    <mergeCell ref="A78:H78"/>
     <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="A62:H63"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A70:G70"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="E3:H3"/>
-    <mergeCell ref="J72:K72"/>
-    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="J70:K70"/>
+    <mergeCell ref="A68:G68"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A63:G63"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A98:H101"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A80:H80"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A60:H61"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3566,24 +3537,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" customWidth="1"/>
-    <col min="14" max="14" width="13.44140625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26.25" customHeight="1">
@@ -3615,7 +3586,7 @@
       <c r="A2" s="61"/>
       <c r="B2" s="61"/>
       <c r="C2" s="124">
-        <v>2283892.2599999998</v>
+        <v>3283892.26</v>
       </c>
       <c r="D2" s="61"/>
       <c r="E2" s="61"/>
@@ -3654,7 +3625,7 @@
     <row r="4" spans="1:17" ht="18.75" customHeight="1">
       <c r="A4" s="118"/>
       <c r="B4" s="119" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C4" s="61"/>
       <c r="D4" s="61"/>
@@ -3681,12 +3652,12 @@
       <c r="A5" s="120"/>
       <c r="B5" s="229">
         <f>C2</f>
-        <v>2283892.2599999998</v>
+        <v>3283892.26</v>
       </c>
       <c r="C5" s="229"/>
       <c r="D5" s="21"/>
       <c r="E5" s="235">
-        <v>278067</v>
+        <v>0</v>
       </c>
       <c r="F5" s="236"/>
       <c r="G5" s="114"/>
@@ -3705,7 +3676,7 @@
       <c r="C6" s="232"/>
       <c r="D6" s="21"/>
       <c r="E6" s="231" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F6" s="232"/>
       <c r="G6" s="114"/>
@@ -3755,19 +3726,19 @@
         <v>16</v>
       </c>
       <c r="G8" s="112" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H8" s="112" t="s">
         <v>63</v>
       </c>
       <c r="I8" s="112" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J8" s="112" t="s">
         <v>64</v>
       </c>
       <c r="K8" s="123" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L8" s="109" t="s">
         <v>82</v>
@@ -3776,7 +3747,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="109" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O8" s="113" t="s">
         <v>8</v>
@@ -3799,22 +3770,22 @@
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="F9" s="98">
-        <v>-103223.45747000005</v>
+        <v>1172.4310599999444</v>
       </c>
       <c r="G9" s="176">
         <v>0</v>
       </c>
       <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
-        <v>0</v>
+        <v>1172.4310599999444</v>
       </c>
       <c r="I9" s="68">
         <f>H9*3.7%</f>
-        <v>0</v>
+        <v>43.379949219997947</v>
       </c>
       <c r="J9" s="68">
         <f>IF(G9&gt;F9,G9-F9,0)</f>
-        <v>103223.45747000005</v>
+        <v>0</v>
       </c>
       <c r="K9" s="68">
         <f>F$4*E9</f>
@@ -3826,7 +3797,7 @@
       </c>
       <c r="M9" s="168">
         <f>B$5*E9</f>
-        <v>92497.636529999989</v>
+        <v>132997.63652999999</v>
       </c>
       <c r="N9" s="168">
         <f>B$7*E9</f>
@@ -3834,7 +3805,7 @@
       </c>
       <c r="O9" s="183">
         <f>H9+I9-J9+K9+M9+N9+L9</f>
-        <v>1172.4310599999444</v>
+        <v>146111.69953921993</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1">
@@ -3852,11 +3823,11 @@
         <v>6.4799999999999996E-2</v>
       </c>
       <c r="F10" s="17">
-        <v>154842.46804799998</v>
+        <v>167033.42164799996</v>
       </c>
       <c r="G10" s="176">
         <f>F10</f>
-        <v>154842.46804799998</v>
+        <v>167033.42164799996</v>
       </c>
       <c r="H10" s="24">
         <f t="shared" ref="H10:H31" si="0">IF(F10&gt;G10,F10-G10,0)</f>
@@ -3880,7 +3851,7 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" ref="M10:M31" si="4">B$5*E10</f>
-        <v>147996.21844799997</v>
+        <v>212796.21844799997</v>
       </c>
       <c r="N10" s="25">
         <f t="shared" ref="N10:N31" si="5">B$7*E10</f>
@@ -3888,7 +3859,7 @@
       </c>
       <c r="O10" s="183">
         <f t="shared" ref="O10:O31" si="6">H10+I10-J10+K10+M10+N10+L10</f>
-        <v>167033.42164799996</v>
+        <v>231833.42164799996</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1">
@@ -3908,11 +3879,11 @@
         <v>4.82E-2</v>
       </c>
       <c r="F11" s="98">
-        <v>115176.03333199999</v>
+        <v>124243.995732</v>
       </c>
       <c r="G11" s="176">
         <f>F11</f>
-        <v>115176.03333199999</v>
+        <v>124243.995732</v>
       </c>
       <c r="H11" s="68">
         <f t="shared" si="0"/>
@@ -3936,7 +3907,7 @@
       </c>
       <c r="M11" s="168">
         <f t="shared" si="4"/>
-        <v>110083.606932</v>
+        <v>158283.606932</v>
       </c>
       <c r="N11" s="168">
         <f t="shared" si="5"/>
@@ -3944,7 +3915,7 @@
       </c>
       <c r="O11" s="183">
         <f t="shared" si="6"/>
-        <v>124243.995732</v>
+        <v>172443.99573199998</v>
       </c>
       <c r="P11" s="171"/>
     </row>
@@ -3965,16 +3936,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F12" s="147">
-        <v>4827387.2296774341</v>
+        <v>5143906.2370854998</v>
       </c>
       <c r="G12" s="177"/>
       <c r="H12" s="148">
         <f t="shared" si="0"/>
-        <v>4827387.2296774341</v>
+        <v>5143906.2370854998</v>
       </c>
       <c r="I12" s="148">
         <f t="shared" si="7"/>
-        <v>178613.32749806507</v>
+        <v>190324.53077216353</v>
       </c>
       <c r="J12" s="148">
         <f t="shared" si="1"/>
@@ -3990,7 +3961,7 @@
       </c>
       <c r="M12" s="149">
         <f t="shared" si="4"/>
-        <v>122188.23590999999</v>
+        <v>175688.23590999999</v>
       </c>
       <c r="N12" s="149">
         <f t="shared" si="5"/>
@@ -3998,7 +3969,7 @@
       </c>
       <c r="O12" s="184">
         <f t="shared" si="6"/>
-        <v>5143906.2370854998</v>
+        <v>5525636.4477676637</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1">
@@ -4016,11 +3987,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F13" s="17">
-        <v>91997.454009999987</v>
+        <v>99240.536009999982</v>
       </c>
       <c r="G13" s="176">
         <f>F13</f>
-        <v>91997.454009999987</v>
+        <v>99240.536009999982</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" si="0"/>
@@ -4044,7 +4015,7 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="4"/>
-        <v>87929.852009999988</v>
+        <v>126429.85200999999</v>
       </c>
       <c r="N13" s="25">
         <f t="shared" si="5"/>
@@ -4052,7 +4023,7 @@
       </c>
       <c r="O13" s="183">
         <f t="shared" si="6"/>
-        <v>99240.536009999982</v>
+        <v>137740.53600999998</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1">
@@ -4065,17 +4036,16 @@
       <c r="C14" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="92" t="s">
-        <v>105</v>
-      </c>
+      <c r="D14" s="92"/>
       <c r="E14" s="45">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F14" s="17">
-        <v>85784.638933999988</v>
+        <v>92523.216667999979</v>
       </c>
       <c r="G14" s="176">
-        <v>85800</v>
+        <f>F14</f>
+        <v>92523.216667999979</v>
       </c>
       <c r="H14" s="24">
         <f t="shared" si="0"/>
@@ -4087,7 +4057,7 @@
       </c>
       <c r="J14" s="24">
         <f t="shared" si="1"/>
-        <v>15.361066000012215</v>
+        <v>0</v>
       </c>
       <c r="K14" s="24">
         <f t="shared" si="2"/>
@@ -4099,7 +4069,7 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="4"/>
-        <v>81991.732133999991</v>
+        <v>117891.73213399999</v>
       </c>
       <c r="N14" s="25">
         <f t="shared" si="5"/>
@@ -4107,7 +4077,7 @@
       </c>
       <c r="O14" s="183">
         <f t="shared" si="6"/>
-        <v>92523.216667999979</v>
+        <v>128438.57773399999</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15" customHeight="1">
@@ -4118,20 +4088,20 @@
         <v>46</v>
       </c>
       <c r="C15" s="93" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D15" s="92" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E15" s="45">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="17">
-        <v>98927.13236399999</v>
+        <v>106715.79716399999</v>
       </c>
       <c r="G15" s="176">
         <f>F15</f>
-        <v>98927.13236399999</v>
+        <v>106715.79716399999</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
@@ -4155,14 +4125,14 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="4"/>
-        <v>94553.139563999983</v>
+        <v>135953.13956399998</v>
       </c>
       <c r="N15" s="25">
         <v>0</v>
       </c>
       <c r="O15" s="183">
         <f t="shared" si="6"/>
-        <v>106715.79716399999</v>
+        <v>148115.79716399999</v>
       </c>
       <c r="Q15" s="180"/>
     </row>
@@ -4177,17 +4147,17 @@
         <v>75</v>
       </c>
       <c r="D16" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E16" s="45">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F16" s="17">
-        <v>127840.61790999999</v>
+        <v>137905.67990999998</v>
       </c>
       <c r="G16" s="176">
         <f>F16</f>
-        <v>127840.61790999999</v>
+        <v>137905.67990999998</v>
       </c>
       <c r="H16" s="24">
         <f t="shared" si="0"/>
@@ -4211,7 +4181,7 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="4"/>
-        <v>122188.23590999999</v>
+        <v>175688.23590999999</v>
       </c>
       <c r="N16" s="25">
         <f t="shared" si="5"/>
@@ -4219,7 +4189,7 @@
       </c>
       <c r="O16" s="183">
         <f t="shared" si="6"/>
-        <v>137905.67990999998</v>
+        <v>191405.67990999998</v>
       </c>
       <c r="Q16" s="180"/>
     </row>
@@ -4234,25 +4204,22 @@
         <v>26</v>
       </c>
       <c r="D17" s="92" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E17" s="45">
         <v>3.85E-2</v>
       </c>
       <c r="F17" s="17">
-        <v>91997.454009999987</v>
-      </c>
-      <c r="G17" s="176">
-        <f>F17</f>
-        <v>91997.454009999987</v>
-      </c>
+        <v>99240.536009999982</v>
+      </c>
+      <c r="G17" s="176"/>
       <c r="H17" s="24">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99240.536009999982</v>
       </c>
       <c r="I17" s="24">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3671.8998323699998</v>
       </c>
       <c r="J17" s="24">
         <f t="shared" si="1"/>
@@ -4268,7 +4235,7 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="4"/>
-        <v>87929.852009999988</v>
+        <v>126429.85200999999</v>
       </c>
       <c r="N17" s="25">
         <f t="shared" si="5"/>
@@ -4276,7 +4243,7 @@
       </c>
       <c r="O17" s="183">
         <f t="shared" si="6"/>
-        <v>99240.536009999982</v>
+        <v>240652.97185236996</v>
       </c>
       <c r="Q17" s="180"/>
     </row>
@@ -4295,11 +4262,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F18" s="98">
-        <v>208542.94590091039</v>
+        <v>77881.52363491038</v>
       </c>
       <c r="G18" s="176">
-        <f>RESUMEN!H37+RESUMEN!H42+RESUMEN!H47+20000</f>
-        <v>223200</v>
+        <f>25000+RESUMEN!H42+RESUMEN!H37</f>
+        <v>183200</v>
       </c>
       <c r="H18" s="68">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
@@ -4311,7 +4278,7 @@
       </c>
       <c r="J18" s="68">
         <f t="shared" si="1"/>
-        <v>14657.054099089612</v>
+        <v>105318.47636508962</v>
       </c>
       <c r="K18" s="68">
         <f t="shared" si="2"/>
@@ -4323,7 +4290,7 @@
       </c>
       <c r="M18" s="168">
         <f t="shared" si="4"/>
-        <v>81991.732133999991</v>
+        <v>117891.73213399999</v>
       </c>
       <c r="N18" s="168">
         <f t="shared" si="5"/>
@@ -4331,7 +4298,7 @@
       </c>
       <c r="O18" s="183">
         <f t="shared" si="6"/>
-        <v>77881.52363491038</v>
+        <v>23120.101368910371</v>
       </c>
       <c r="Q18" s="180"/>
     </row>
@@ -4346,22 +4313,22 @@
         <v>28</v>
       </c>
       <c r="D19" s="153" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E19" s="154">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F19" s="147">
-        <v>3398187.1849690727</v>
+        <v>3630635.9079769286</v>
       </c>
       <c r="G19" s="177"/>
       <c r="H19" s="148">
         <f t="shared" si="0"/>
-        <v>3398187.1849690727</v>
+        <v>3630635.9079769286</v>
       </c>
       <c r="I19" s="148">
         <f t="shared" si="7"/>
-        <v>125732.9258438557</v>
+        <v>134333.52859514637</v>
       </c>
       <c r="J19" s="148">
         <f t="shared" si="1"/>
@@ -4377,7 +4344,7 @@
       </c>
       <c r="M19" s="149">
         <f t="shared" si="4"/>
-        <v>94553.139563999983</v>
+        <v>135953.13956399998</v>
       </c>
       <c r="N19" s="149">
         <f t="shared" si="5"/>
@@ -4385,7 +4352,7 @@
       </c>
       <c r="O19" s="184">
         <f t="shared" si="6"/>
-        <v>3630635.9079769286</v>
+        <v>3913085.233736075</v>
       </c>
       <c r="Q19" s="180"/>
     </row>
@@ -4397,20 +4364,20 @@
         <v>51</v>
       </c>
       <c r="C20" s="100" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D20" s="96" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E20" s="46">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F20" s="17">
-        <v>127840.61790999999</v>
+        <v>137905.67990999998</v>
       </c>
       <c r="G20" s="176">
         <f>F20</f>
-        <v>127840.61790999999</v>
+        <v>137905.67990999998</v>
       </c>
       <c r="H20" s="24">
         <f t="shared" si="0"/>
@@ -4434,7 +4401,7 @@
       </c>
       <c r="M20" s="25">
         <f t="shared" si="4"/>
-        <v>122188.23590999999</v>
+        <v>175688.23590999999</v>
       </c>
       <c r="N20" s="25">
         <f t="shared" si="5"/>
@@ -4442,7 +4409,7 @@
       </c>
       <c r="O20" s="183">
         <f t="shared" si="6"/>
-        <v>137905.67990999998</v>
+        <v>191405.67990999998</v>
       </c>
       <c r="Q20" s="180"/>
     </row>
@@ -4461,18 +4428,18 @@
         <v>3.85E-2</v>
       </c>
       <c r="F21" s="147">
-        <v>1411097.1317416991</v>
+        <v>1562548.2616261418</v>
       </c>
       <c r="G21" s="178">
         <v>0</v>
       </c>
       <c r="H21" s="148">
         <f t="shared" si="0"/>
-        <v>1411097.1317416991</v>
+        <v>1562548.2616261418</v>
       </c>
       <c r="I21" s="148">
         <f t="shared" si="7"/>
-        <v>52210.593874442871</v>
+        <v>57814.285680167253</v>
       </c>
       <c r="J21" s="148">
         <f t="shared" si="1"/>
@@ -4488,7 +4455,7 @@
       </c>
       <c r="M21" s="149">
         <f t="shared" si="4"/>
-        <v>87929.852009999988</v>
+        <v>126429.85200999999</v>
       </c>
       <c r="N21" s="149">
         <f t="shared" si="5"/>
@@ -4496,7 +4463,7 @@
       </c>
       <c r="O21" s="184">
         <f t="shared" si="6"/>
-        <v>1562548.2616261418</v>
+        <v>1758103.0833163089</v>
       </c>
       <c r="Q21" s="180"/>
     </row>
@@ -4511,17 +4478,17 @@
         <v>31</v>
       </c>
       <c r="D22" s="93" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E22" s="47">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F22" s="17">
-        <v>85784.638933999988</v>
+        <v>92538.577733999991</v>
       </c>
       <c r="G22" s="176">
         <f>F22</f>
-        <v>85784.638933999988</v>
+        <v>92538.577733999991</v>
       </c>
       <c r="H22" s="24">
         <f t="shared" si="0"/>
@@ -4545,7 +4512,7 @@
       </c>
       <c r="M22" s="25">
         <f t="shared" si="4"/>
-        <v>81991.732133999991</v>
+        <v>117891.73213399999</v>
       </c>
       <c r="N22" s="25">
         <f t="shared" si="5"/>
@@ -4553,7 +4520,7 @@
       </c>
       <c r="O22" s="183">
         <f t="shared" si="6"/>
-        <v>92538.577733999991</v>
+        <v>128438.57773399999</v>
       </c>
       <c r="Q22" s="180"/>
     </row>
@@ -4568,17 +4535,17 @@
         <v>32</v>
       </c>
       <c r="D23" s="94" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E23" s="48">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F23" s="17">
-        <v>98927.13236399999</v>
+        <v>106715.79716399999</v>
       </c>
       <c r="G23" s="176">
         <f>F23</f>
-        <v>98927.13236399999</v>
+        <v>106715.79716399999</v>
       </c>
       <c r="H23" s="24">
         <f t="shared" si="0"/>
@@ -4602,7 +4569,7 @@
       </c>
       <c r="M23" s="25">
         <f t="shared" si="4"/>
-        <v>94553.139563999983</v>
+        <v>135953.13956399998</v>
       </c>
       <c r="N23" s="25">
         <f t="shared" si="5"/>
@@ -4610,7 +4577,7 @@
       </c>
       <c r="O23" s="183">
         <f t="shared" si="6"/>
-        <v>106715.79716399999</v>
+        <v>148115.79716399999</v>
       </c>
       <c r="Q23" s="180"/>
     </row>
@@ -4629,11 +4596,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F24" s="17">
-        <v>127840.61790999999</v>
+        <v>137905.67990999998</v>
       </c>
       <c r="G24" s="176">
         <f>F24</f>
-        <v>127840.61790999999</v>
+        <v>137905.67990999998</v>
       </c>
       <c r="H24" s="24">
         <f t="shared" si="0"/>
@@ -4657,7 +4624,7 @@
       </c>
       <c r="M24" s="25">
         <f t="shared" si="4"/>
-        <v>122188.23590999999</v>
+        <v>175688.23590999999</v>
       </c>
       <c r="N24" s="25">
         <f t="shared" si="5"/>
@@ -4665,7 +4632,7 @@
       </c>
       <c r="O24" s="183">
         <f t="shared" si="6"/>
-        <v>137905.67990999998</v>
+        <v>191405.67990999998</v>
       </c>
       <c r="Q24" s="180"/>
     </row>
@@ -4680,17 +4647,17 @@
         <v>91</v>
       </c>
       <c r="D25" s="95" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E25" s="49">
         <v>3.85E-2</v>
       </c>
       <c r="F25" s="17">
-        <v>91997.454009999987</v>
+        <v>99240.536009999982</v>
       </c>
       <c r="G25" s="176">
         <f>F25</f>
-        <v>91997.454009999987</v>
+        <v>99240.536009999982</v>
       </c>
       <c r="H25" s="24">
         <f t="shared" si="0"/>
@@ -4714,7 +4681,7 @@
       </c>
       <c r="M25" s="25">
         <f t="shared" si="4"/>
-        <v>87929.852009999988</v>
+        <v>126429.85200999999</v>
       </c>
       <c r="N25" s="25">
         <f t="shared" si="5"/>
@@ -4722,7 +4689,7 @@
       </c>
       <c r="O25" s="183">
         <f t="shared" si="6"/>
-        <v>99240.536009999982</v>
+        <v>137740.53600999998</v>
       </c>
       <c r="Q25" s="181"/>
     </row>
@@ -4741,11 +4708,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F26" s="17">
-        <v>85784.638933999988</v>
+        <v>92538.577733999991</v>
       </c>
       <c r="G26" s="176">
         <f>F26</f>
-        <v>85784.638933999988</v>
+        <v>92538.577733999991</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="0"/>
@@ -4769,7 +4736,7 @@
       </c>
       <c r="M26" s="25">
         <f t="shared" si="4"/>
-        <v>81991.732133999991</v>
+        <v>117891.73213399999</v>
       </c>
       <c r="N26" s="25">
         <f t="shared" si="5"/>
@@ -4777,7 +4744,7 @@
       </c>
       <c r="O26" s="183">
         <f t="shared" si="6"/>
-        <v>92538.577733999991</v>
+        <v>128438.57773399999</v>
       </c>
       <c r="Q26" s="180"/>
     </row>
@@ -4792,24 +4759,24 @@
         <v>35</v>
       </c>
       <c r="D27" s="145" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E27" s="146">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F27" s="147">
-        <v>3275871.2751196874</v>
+        <v>3401206.8652831158</v>
       </c>
       <c r="G27" s="177">
-        <v>98927.14</v>
+        <v>106800</v>
       </c>
       <c r="H27" s="170">
         <f t="shared" si="0"/>
-        <v>3176944.1351196873</v>
+        <v>3294406.8652831158</v>
       </c>
       <c r="I27" s="148">
         <f t="shared" si="7"/>
-        <v>117546.93299942845</v>
+        <v>121893.0540154753</v>
       </c>
       <c r="J27" s="148">
         <f t="shared" si="1"/>
@@ -4825,7 +4792,7 @@
       </c>
       <c r="M27" s="149">
         <f t="shared" si="4"/>
-        <v>94553.139563999983</v>
+        <v>135953.13956399998</v>
       </c>
       <c r="N27" s="149">
         <f t="shared" si="5"/>
@@ -4833,11 +4800,11 @@
       </c>
       <c r="O27" s="184">
         <f t="shared" si="6"/>
-        <v>3401206.8652831158</v>
+        <v>3564415.7164625912</v>
       </c>
       <c r="P27" s="182">
         <f>M27+N27</f>
-        <v>94553.139563999983</v>
+        <v>135953.13956399998</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="17.25" customHeight="1">
@@ -4855,16 +4822,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
-        <v>2547550.7298982162</v>
+        <v>2763998.3428144502</v>
       </c>
       <c r="G28" s="176"/>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
-        <v>2547550.7298982162</v>
+        <v>2763998.3428144502</v>
       </c>
       <c r="I28" s="24">
         <f t="shared" si="7"/>
-        <v>94259.377006234019</v>
+        <v>102267.93868413467</v>
       </c>
       <c r="J28" s="24">
         <f t="shared" si="1"/>
@@ -4877,7 +4844,7 @@
       </c>
       <c r="M28" s="25">
         <f t="shared" si="4"/>
-        <v>122188.23590999999</v>
+        <v>175688.23590999999</v>
       </c>
       <c r="N28" s="25">
         <f t="shared" si="5"/>
@@ -4885,7 +4852,7 @@
       </c>
       <c r="O28" s="183">
         <f t="shared" si="6"/>
-        <v>2763998.3428144502</v>
+        <v>3041954.5174085847</v>
       </c>
       <c r="P28" s="7"/>
     </row>
@@ -4904,11 +4871,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F29" s="17">
-        <v>91997.454009999987</v>
+        <v>99240.536009999982</v>
       </c>
       <c r="G29" s="176">
         <f>F29</f>
-        <v>91997.454009999987</v>
+        <v>99240.536009999982</v>
       </c>
       <c r="H29" s="24">
         <f t="shared" si="0"/>
@@ -4932,7 +4899,7 @@
       </c>
       <c r="M29" s="25">
         <f t="shared" si="4"/>
-        <v>87929.852009999988</v>
+        <v>126429.85200999999</v>
       </c>
       <c r="N29" s="25">
         <f t="shared" si="5"/>
@@ -4940,18 +4907,18 @@
       </c>
       <c r="O29" s="183">
         <f t="shared" si="6"/>
-        <v>99240.536009999982</v>
+        <v>137740.53600999998</v>
       </c>
       <c r="P29" s="7">
         <f>M29/2</f>
-        <v>43964.926004999994</v>
+        <v>63214.926004999994</v>
       </c>
       <c r="Q29" s="7">
         <f>SUM(Q15:Q28)</f>
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1">
@@ -4962,20 +4929,20 @@
         <v>61</v>
       </c>
       <c r="C30" s="95" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D30" s="95" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E30" s="49">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F30" s="17">
-        <v>85784.638933999988</v>
+        <v>92538.577733999991</v>
       </c>
       <c r="G30" s="176">
         <f>F30</f>
-        <v>85784.638933999988</v>
+        <v>92538.577733999991</v>
       </c>
       <c r="H30" s="24">
         <f t="shared" si="0"/>
@@ -4999,7 +4966,7 @@
       </c>
       <c r="M30" s="25">
         <f t="shared" si="4"/>
-        <v>81991.732133999991</v>
+        <v>117891.73213399999</v>
       </c>
       <c r="N30" s="25">
         <f t="shared" si="5"/>
@@ -5007,7 +4974,7 @@
       </c>
       <c r="O30" s="183">
         <f t="shared" si="6"/>
-        <v>92538.577733999991</v>
+        <v>128438.57773399999</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1">
@@ -5025,11 +4992,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F31" s="17">
-        <v>98927.13236399999</v>
+        <v>106715.79716399999</v>
       </c>
       <c r="G31" s="176">
         <f>F31</f>
-        <v>98927.13236399999</v>
+        <v>106715.79716399999</v>
       </c>
       <c r="H31" s="24">
         <f t="shared" si="0"/>
@@ -5053,7 +5020,7 @@
       </c>
       <c r="M31" s="25">
         <f t="shared" si="4"/>
-        <v>94553.139563999983</v>
+        <v>135953.13956399998</v>
       </c>
       <c r="N31" s="25">
         <f t="shared" si="5"/>
@@ -5061,10 +5028,10 @@
       </c>
       <c r="O31" s="183">
         <f t="shared" si="6"/>
-        <v>106715.79716399999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="15.6">
+        <v>148115.79716399999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -5078,23 +5045,23 @@
       </c>
       <c r="F32" s="99">
         <f>SUM(F9:F31)</f>
-        <v>17226863.163815022</v>
+        <v>18373592.511993047</v>
       </c>
       <c r="G32" s="99">
-        <f>SUM(G9:G31)</f>
-        <v>1983592.6250439996</v>
+        <f>SUM(G9:G31)-428650</f>
+        <v>1554352.4065020001</v>
       </c>
       <c r="H32" s="122">
         <f>SUM(H9:H31)</f>
-        <v>15361166.411406109</v>
+        <v>16495908.581856135</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>568363.15722202614</v>
+        <v>610348.6175286771</v>
       </c>
       <c r="J32" s="99">
         <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
-        <v>117895.87263508968</v>
+        <v>105318.47636508962</v>
       </c>
       <c r="K32" s="90">
         <f>SUM(K9:K31)</f>
@@ -5103,7 +5070,7 @@
       <c r="L32" s="90"/>
       <c r="M32" s="54">
         <f>SUM(M9:M31)</f>
-        <v>2283892.2599999998</v>
+        <v>3283892.26</v>
       </c>
       <c r="N32" s="90">
         <f>SUM(N9:N31)</f>
@@ -5111,7 +5078,7 @@
       </c>
       <c r="O32" s="54">
         <f>SUM(O9:O31)</f>
-        <v>18373592.511993047</v>
+        <v>20562897.539019726</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="14.25" customHeight="1"/>
@@ -5253,13 +5220,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.109375" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
@@ -5307,13 +5274,13 @@
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1">
       <c r="A7" s="62"/>
       <c r="B7" s="32"/>
       <c r="C7" s="16"/>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" ht="29.4" thickBot="1">
+    <row r="8" spans="1:7" ht="30.75" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>0</v>
       </c>
@@ -5674,7 +5641,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6">
+    <row r="24" spans="1:7" ht="15.75">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -5696,7 +5663,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6">
+    <row r="25" spans="1:7" ht="15.75">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -5718,7 +5685,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.6">
+    <row r="26" spans="1:7" ht="15.75">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -5740,7 +5707,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.6">
+    <row r="27" spans="1:7" ht="15.75">
       <c r="A27" s="51">
         <v>19</v>
       </c>
@@ -5766,7 +5733,7 @@
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6">
+    <row r="28" spans="1:7" ht="15.75">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -5788,7 +5755,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.6">
+    <row r="29" spans="1:7" ht="15.75">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -5810,7 +5777,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.6">
+    <row r="30" spans="1:7" ht="15.75">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -5832,7 +5799,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.6">
+    <row r="31" spans="1:7" ht="15.75">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -5854,7 +5821,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.6">
+    <row r="32" spans="1:7" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
